--- a/Perhitungan_SPK_TravelFit.xlsx
+++ b/Perhitungan_SPK_TravelFit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\SPK_Destinasi_Wisata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8F79A1-15DD-40DE-8429-35CE9695EB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EC33B1-D6AB-4E42-A741-0670DC1F734B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -1745,7 +1745,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="7" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
@@ -7520,15 +7522,15 @@
   <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="1" max="1" width="108.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.25">
@@ -7564,7 +7566,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>260</v>
       </c>
